--- a/public/example-students.xlsx
+++ b/public/example-students.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus Tuf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FE-JoniHalim\New 2026\admin_web_stain\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F60D728F-A40E-4462-AD1D-F821025D18FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41B0BFB-06B3-4406-AB9C-938FE878E517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7DA0C62D-C919-43B5-B561-BEA4D61275D9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>NIM</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>ibu jokowie</t>
+  </si>
+  <si>
+    <t>ID_STATUS</t>
+  </si>
+  <si>
+    <t>b0a2ea5e-e537-4e35-acae-baf7c4b061dc</t>
   </si>
 </sst>
 </file>
@@ -510,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBD5FB1-0927-40B1-A849-455336DF6EFB}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="39.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -523,17 +529,18 @@
     <col min="8" max="8" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="39" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="11" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -565,28 +572,31 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -617,28 +627,31 @@
       <c r="J2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{09B602C9-4C85-4D7B-ACA6-32C539C9FB8F}"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{09B602C9-4C85-4D7B-ACA6-32C539C9FB8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
